--- a/inventory_by_bunker/BUNKER 2968 Laredo.xlsx
+++ b/inventory_by_bunker/BUNKER 2968 Laredo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bunker de Refacciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{978E6EB4-BE34-4EBF-B254-2A55791D1571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62913323-43DF-4772-B376-B853786222C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{506D2D55-3137-420B-8BEA-69CDDEA128A9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{506D2D55-3137-420B-8BEA-69CDDEA128A9}"/>
   </bookViews>
   <sheets>
     <sheet name="2968" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <definedName name="Solicitante">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="116">
   <si>
     <t>Cantidad</t>
   </si>
@@ -60,48 +59,24 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>Descripción</t>
-  </si>
-  <si>
     <t>Fabricante</t>
   </si>
   <si>
     <t>Modelo</t>
   </si>
   <si>
-    <t>Serie/ #parte</t>
-  </si>
-  <si>
     <t>Condicion</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
     <t>Funcional</t>
   </si>
   <si>
-    <t>TECLADOS</t>
-  </si>
-  <si>
-    <t>TECLADOS PC</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>BIZERBA</t>
-  </si>
-  <si>
-    <t>CARRITO IMPRESOR</t>
-  </si>
-  <si>
-    <t>CARRITO</t>
-  </si>
-  <si>
     <t>FUSING DRIVER</t>
   </si>
   <si>
@@ -114,33 +89,12 @@
     <t>Thin Client</t>
   </si>
   <si>
-    <t>hp</t>
-  </si>
-  <si>
     <t>8CN01704QZ</t>
   </si>
   <si>
-    <t>t630</t>
-  </si>
-  <si>
     <t>8CN01704R7</t>
   </si>
   <si>
-    <t>8CN003030S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15MT </t>
-  </si>
-  <si>
-    <t>CABLE ETHERNET</t>
-  </si>
-  <si>
-    <t>TACLADO POS</t>
-  </si>
-  <si>
-    <t>TECLADOS POS</t>
-  </si>
-  <si>
     <t>PrehKeyTec</t>
   </si>
   <si>
@@ -150,30 +104,12 @@
     <t>1768155</t>
   </si>
   <si>
-    <t>FILMINA</t>
-  </si>
-  <si>
-    <t>MONITOR</t>
-  </si>
-  <si>
-    <t>MONITOR POS</t>
-  </si>
-  <si>
     <t>HP 322pv</t>
   </si>
   <si>
     <t>CNK44007VN</t>
   </si>
   <si>
-    <t>IMPRSORA TERMICA</t>
-  </si>
-  <si>
-    <t>IMPRESORA</t>
-  </si>
-  <si>
-    <t>EPSON</t>
-  </si>
-  <si>
     <t>TM-T88V1</t>
   </si>
   <si>
@@ -186,15 +122,6 @@
     <t>XAYW000923</t>
   </si>
   <si>
-    <t>RADIO</t>
-  </si>
-  <si>
-    <t>RADIO COMUNICACION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOTOROLA </t>
-  </si>
-  <si>
     <t>DEP 450</t>
   </si>
   <si>
@@ -216,21 +143,12 @@
     <t>752TVFA707</t>
   </si>
   <si>
-    <t>BASCULA ETIQUETADORA</t>
-  </si>
-  <si>
     <t>BASCULA</t>
   </si>
   <si>
-    <t>XC II PRO</t>
-  </si>
-  <si>
     <t>20323395</t>
   </si>
   <si>
-    <t>XC MODULAR</t>
-  </si>
-  <si>
     <t>20262625</t>
   </si>
   <si>
@@ -252,9 +170,6 @@
     <t>P5TF156825</t>
   </si>
   <si>
-    <t>iImpresora Laser</t>
-  </si>
-  <si>
     <t>LaserJet Enterprise M506</t>
   </si>
   <si>
@@ -264,9 +179,6 @@
     <t>JPDCL270MY</t>
   </si>
   <si>
-    <t xml:space="preserve">Kit mtto 806 </t>
-  </si>
-  <si>
     <t xml:space="preserve">PC Completa </t>
   </si>
   <si>
@@ -300,15 +212,6 @@
     <t>Caja FS</t>
   </si>
   <si>
-    <t>Clavija Nema L5-15</t>
-  </si>
-  <si>
-    <t>Contacto Nema L5-15 c/ tapa</t>
-  </si>
-  <si>
-    <t>Báscula Toledo Completa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Membrana Toledo </t>
   </si>
   <si>
@@ -336,18 +239,6 @@
     <t>Telefonos Análogos</t>
   </si>
   <si>
-    <t>kit mtto m806</t>
-  </si>
-  <si>
-    <t>mouse</t>
-  </si>
-  <si>
-    <t>IMPRESORA PORTATIL</t>
-  </si>
-  <si>
-    <t>ZEBRA</t>
-  </si>
-  <si>
     <t>ZQ620</t>
   </si>
   <si>
@@ -384,24 +275,6 @@
     <t>8CN1100147</t>
   </si>
   <si>
-    <t>t640</t>
-  </si>
-  <si>
-    <t>100 pza's</t>
-  </si>
-  <si>
-    <t>falta</t>
-  </si>
-  <si>
-    <t>Contacto Nema L5-15</t>
-  </si>
-  <si>
-    <t>PANDUIT</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
     <t>BPRO</t>
   </si>
   <si>
@@ -414,14 +287,125 @@
     <t>RM1'9788'000</t>
   </si>
   <si>
-    <t>NUEVO</t>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>Teclado Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresor </t>
+  </si>
+  <si>
+    <t>Bizerba</t>
+  </si>
+  <si>
+    <t>T630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panduit </t>
+  </si>
+  <si>
+    <t>Teclado POS</t>
+  </si>
+  <si>
+    <t>Filmina</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Impresora Termica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impresora </t>
+  </si>
+  <si>
+    <t>Impresora</t>
+  </si>
+  <si>
+    <t>Epson</t>
+  </si>
+  <si>
+    <t>Radiofrecuencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bascula Etiquetadora </t>
+  </si>
+  <si>
+    <t>Bascula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bascula </t>
+  </si>
+  <si>
+    <t>Impresora Laser</t>
+  </si>
+  <si>
+    <t>Kit de Mantenimiento</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Impresora Portatil</t>
+  </si>
+  <si>
+    <t>Zebra</t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>Panduit</t>
+  </si>
+  <si>
+    <t>Clavija de Seguridad</t>
+  </si>
+  <si>
+    <t>Nema L5-15</t>
+  </si>
+  <si>
+    <t>Eaton</t>
+  </si>
+  <si>
+    <t>Contacto de Seguridad</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>Tapa Contacto de Seguridad</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>Bateria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola </t>
+  </si>
+  <si>
+    <t>XC115E PRO</t>
+  </si>
+  <si>
+    <t>XC115E  MODULAR</t>
+  </si>
+  <si>
+    <t>XC115E MODULAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -433,6 +417,11 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -447,13 +436,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <fgColor theme="3" tint="0.249977111117893"/>
         <bgColor theme="8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <fgColor theme="3" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,13 +476,13 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -863,7 +852,7 @@
   <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
     <col min="2" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.1796875" bestFit="1" customWidth="1"/>
@@ -879,19 +868,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -899,22 +888,22 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -922,22 +911,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -945,22 +934,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -968,22 +957,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -991,22 +980,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1014,22 +1003,22 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1037,22 +1026,22 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1060,45 +1049,45 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="1">
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1106,22 +1095,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1129,22 +1118,22 @@
         <v>2</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1152,22 +1141,22 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1175,22 +1164,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1198,22 +1187,22 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1221,22 +1210,22 @@
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1244,22 +1233,22 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1267,22 +1256,22 @@
         <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1290,22 +1279,22 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1313,22 +1302,22 @@
         <v>1</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1336,22 +1325,22 @@
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1359,22 +1348,22 @@
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -1382,22 +1371,22 @@
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -1405,22 +1394,22 @@
         <v>1</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1428,22 +1417,22 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1451,22 +1440,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1474,22 +1463,22 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -1497,22 +1486,22 @@
         <v>1</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1520,22 +1509,22 @@
         <v>1</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1543,22 +1532,22 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1566,22 +1555,22 @@
         <v>0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -1589,60 +1578,68 @@
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>0</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>0</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -1650,22 +1647,22 @@
         <v>3</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -1673,22 +1670,22 @@
         <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -1696,22 +1693,22 @@
         <v>1</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -1719,22 +1716,22 @@
         <v>1</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
@@ -1742,22 +1739,22 @@
         <v>1</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
@@ -1765,22 +1762,22 @@
         <v>1</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -1788,22 +1785,22 @@
         <v>1</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
@@ -1811,22 +1808,22 @@
         <v>1</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -1834,22 +1831,22 @@
         <v>3</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -1857,22 +1854,22 @@
         <v>5</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -1880,66 +1877,68 @@
         <v>5</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>111</v>
+      <c r="A46" s="1">
+        <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>25</v>
+      <c r="A47" s="1">
+        <v>15</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D47" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -1947,22 +1946,22 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -1970,20 +1969,22 @@
         <v>4</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -1991,20 +1992,22 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D50" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="E50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -2012,20 +2015,22 @@
         <v>3</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51" s="1"/>
+        <v>107</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>12</v>
+        <v>105</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -2033,20 +2038,22 @@
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" s="1"/>
+        <v>109</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -2054,20 +2061,22 @@
         <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" s="1"/>
+        <v>94</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -2075,22 +2084,22 @@
         <v>2</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -2098,22 +2107,22 @@
         <v>2</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F55" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -2121,22 +2130,22 @@
         <v>1</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -2144,22 +2153,22 @@
         <v>2</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -2167,22 +2176,22 @@
         <v>1</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>115</v>
+        <v>94</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -2190,22 +2199,22 @@
         <v>7</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F59" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -2213,45 +2222,45 @@
         <v>1</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F60" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>112</v>
+      <c r="A61" s="3">
+        <v>1</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F61" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -2259,21 +2268,26 @@
         <v>0</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="F1">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>1.01709E+23</formula>
